--- a/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E7A3532-F5A4-4F3A-8F79-A47452EF704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9003E720-4E60-49CC-8C1E-6EBA19DD2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2480,7 +2480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E5C7ED5-A749-4CE3-AEB2-7BBA0CABFB71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D1E97D-4FFE-4F0C-B896-D0E15C33595D}">
   <dimension ref="B2:AF302"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7991,7 +7991,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F4441E-26D1-455A-A53D-1DB7FD333DE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281E1034-DB01-4DBA-A919-4CD8A1BCE96B}">
   <dimension ref="B9:L14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17392,7 +17392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC42714D-9292-4D44-84F3-A355F91C3542}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343BB68E-0BDD-4859-BA54-4AB9A6511595}">
   <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
